--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:43:27+00:00</t>
+    <t>2026-07-01T12:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:03:19+00:00</t>
+    <t>2026-07-03T07:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -919,7 +919,7 @@
     <t>Description of clinical condition indicating why the ImagingStudy was requested.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-imagerie-objectif-reference-cisis|20260420150250</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-imagerie-objectif-reference-cisis|20260619134042</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1206,7 +1206,7 @@
     <t>The laterality of the (possibly paired) anatomic structures examined. E.g., the left knee, both lungs, or unpaired abdomen. If present, shall be consistent with any laterality information indicated in ImagingStudy.series.bodySite.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modificateur-topographique-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modificateur-topographique-cisis|20260619134042</t>
   </si>
   <si>
     <t>(0020,0060)</t>
@@ -1403,7 +1403,7 @@
     <t>DICOM instance  type.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-sop-class-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-sop-class-cisis|20260619134042</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP]. source[classCode=OBS, moodCode=EVN, code="sop class"].value</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:33:59+00:00</t>
+    <t>2026-07-08T09:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T09:43:12+00:00</t>
+    <t>2026-07-08T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
